--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92785</v>
+        <v>92787</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92787</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92791</v>
+        <v>92792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92802</v>
+        <v>92804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92804</v>
+        <v>92817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>92822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92822</v>
+        <v>92832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92833</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2024 artfynd.xlsx
+++ b/artfynd/A 38802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136790857</v>
       </c>
       <c r="B2" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
